--- a/foundational_model_token_usage_by_cloud_provider.xlsx
+++ b/foundational_model_token_usage_by_cloud_provider.xlsx
@@ -8,13 +8,14 @@
   </bookViews>
   <sheets>
     <sheet name="Training Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Inference Pricing" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Inference Volume" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Cloud Partnerships" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Training vs Inference Split" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Hyperscaler CapEx" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Cloud-Model Matrix" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Sources &amp; Methodology" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Token Types &amp; Revenue" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Inference Pricing" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Inference Volume" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Cloud Partnerships" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Training vs Inference Split" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Hyperscaler CapEx" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cloud-Model Matrix" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Sources &amp; Methodology" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,8 +38,13 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -63,6 +69,12 @@
         <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+        <bgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -82,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +108,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1665,6 +1681,2502 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="65" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="60" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>SECTION A: Token Type Definitions &amp; Market Sizing</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="n"/>
+      <c r="C1" s="6" t="n"/>
+      <c r="D1" s="6" t="n"/>
+      <c r="E1" s="6" t="n"/>
+      <c r="F1" s="6" t="n"/>
+      <c r="G1" s="6" t="n"/>
+      <c r="H1" s="6" t="n"/>
+      <c r="I1" s="6" t="n"/>
+      <c r="J1" s="6" t="n"/>
+      <c r="K1" s="6" t="n"/>
+    </row>
+    <row r="2" ht="60" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Token Type</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Typical Volume per Model Run</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Key Models / Use Cases</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Cost Driver</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>Pricing Range ($/1M tokens)</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>% of Total AI Compute (2026 Est.)</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>Market Size (2026 Est.)</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>Growth Rate (CAGR)</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>Token Multiplier vs Single-Shot</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>Key Trend</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Pre-Training Tokens</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Tokens consumed during initial foundation model training on massive text corpora (next-token prediction). One-time cost per model version.</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>1T - 20T+ tokens per model</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>GPT-4 (~16T), Llama 3.1 (15.1T), DeepSeek-V3 (14.8T), Gemini Ultra (~10T+)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>GPU-hours on large clusters (months); hardware cost dominates</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>N/A (internal cost: $3M-$200M+ per model)</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>~15-20%</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>$30-50B (infrastructure spend allocated to pre-training)</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>~25% (driven by larger models &amp; more frequent retraining)</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>N/A (baseline cost, not per-query)</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Costs decreasing per token due to hardware efficiency; total spend increasing as models grow larger</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Post-Training Tokens (SFT / RLHF / DPO / RFT)</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Tokens consumed during supervised fine-tuning, reinforcement learning from human feedback, direct preference optimization, and reinforcement fine-tuning. Includes enterprise custom fine-tuning.</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>10M - 500B tokens per fine-tuning run</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Azure OpenAI fine-tuning, AWS Bedrock RFT, Claude fine-tuning (limited), Gemini tuning</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Smaller datasets but repeated iterations; reward model training; human annotation costs</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Training: $0.15-$15 /1M tokens
+Hosting: $1,836/mo per model (Azure)
+RFT: $100/hr compute (OpenAI)</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>~3-5%</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>$5-10B</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>~30-35% (fastest growth; enterprise customization demand)</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>0.01-0.1x volume of pre-training; 10-100x more iterations than single runs</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Shift to parameter-efficient methods (LoRA/QLoRA); RFT replacing traditional RLHF; token-based billing replacing hourly</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Single-Shot Inference Tokens (Standard)</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Tokens consumed during standard one-pass inference: input prompt + output completion. No internal reasoning loop. Includes chat, completion, embedding, and retrieval queries.</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>500 - 100K tokens per request</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>GPT-4.1, Claude Sonnet 4.5, Gemini Flash, Llama inference, DeepSeek Chat</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Latency-sensitive; per-token compute; output tokens 3-5x more expensive than input</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Input: $0.10-$5.00
+Output: $0.40-$25.00</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>~45-50%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>$35-45B</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>~19% (bulk of current inference market)</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1x (baseline)</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Prices collapsed ~1,000x since 2022; MoE architectures reducing cost 3-5x; batch inference at 50% discount</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Reasoning Tokens (Chain-of-Thought / Thinking)</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Hidden internal tokens generated by reasoning models before producing visible output. Billed as output tokens but not shown to user. Used for multi-step problem decomposition.</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>1K - 100K+ reasoning tokens per request (on top of standard I/O)</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>OpenAI o1/o3/o4-mini, DeepSeek-R1, Claude extended thinking, Gemini thinking mode</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Multiple inference passes; extended compute time; reasoning tokens billed at output rates</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Reasoning output: $2.19-$60.00
+(o3: $8/1M, R1: $2.19/1M, o1: $60/1M)</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>~10-15%</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>$8-15B (growing rapidly)</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>~35-40% (fastest-growing inference segment)</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>3-50x total tokens vs single-shot (problem-dependent)</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Reasoning models growing to dominate complex tasks; DeepSeek R1 96% cheaper than o1; agentic workflows multiplying reasoning token consumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1"/>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>SECTION B: Estimated Token Usage by Model Company &amp; Token Type (Annual, 2025)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="6" t="n"/>
+      <c r="J8" s="6" t="n"/>
+      <c r="K8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>Pre-Training Tokens (Annual Est.)</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>Pre-Training Cost (Annual Est.)</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>Post-Training Tokens (Annual Est.)</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>Post-Training Cost (Annual Est.)</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>Single-Shot Inference Tokens (Annual Est.)</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="inlineStr">
+        <is>
+          <t>Single-Shot Inference Revenue (Annual Est.)</t>
+        </is>
+      </c>
+      <c r="H9" s="1" t="inlineStr">
+        <is>
+          <t>Reasoning Inference Tokens (Annual Est.)</t>
+        </is>
+      </c>
+      <c r="I9" s="1" t="inlineStr">
+        <is>
+          <t>Reasoning Inference Revenue (Annual Est.)</t>
+        </is>
+      </c>
+      <c r="J9" s="1" t="inlineStr">
+        <is>
+          <t>Total Inference Revenue (Annual Est.)</t>
+        </is>
+      </c>
+      <c r="K9" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>~30-50T (GPT-5.x family retraining + variants)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>$500M-$1B+</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>~1-5T (RLHF, RFT, SFT for o-series + GPT fine-tuning)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>$100-300M</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>~2,500T (ChatGPT + API standard models)</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>$6-8B</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>~600-900T (o1, o3, o4-mini reasoning)</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>$4-6B</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>$10-14B</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Total 2025 revenue ~$13-20B; inference cost on Azure ~$12B+; reasoning models are highest revenue per token</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>~15-30T (Claude 3.x, 4.x family)</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>$200-500M</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>~0.5-2T (Constitutional AI, RLHF, preference training)</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>$50-150M</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>~800-1,200T (Claude API + Bedrock + Vertex)</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>$3-5B</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>~200-400T (extended thinking mode)</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>$1.5-3B</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>$4.5-8B</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>ARR surpassed $9B Jan 2026; multi-cloud inference (AWS, GCP, Azure); extended thinking growing</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Google (Gemini)</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>~20-40T (Gemini 3.x family + experimental)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>$300-600M</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>~2-5T (instruction tuning, safety, product-specific fine-tuning)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>$100-250M</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>~14,000T (Search AI, Gmail, YouTube, Workspace, API)</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Embedded in Google Cloud (~$12-18B AI segment)</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>~1,500-2,500T (Gemini thinking mode + Search reasoning)</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Embedded (~$2-4B est.)</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>$14-22B (embedded + API)</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1.3 quadrillion tokens/month; majority from internal product integration; 7B tokens/min via API</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Meta (Llama)</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>~20-40T (Llama 4.x family + research)</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>$300-600M</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>~1-3T (internal RLHF + community fine-tuning)</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>$50-200M</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>~1,500-3,000T (ecosystem-wide: self-hosted + cloud)</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Open-weight (no direct token revenue)</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>~100-300T (Llama reasoning variants)</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Open-weight (no direct token revenue)</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>N/A (monetized via Meta products)</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Most widely deployed open-weight model; no direct token revenue; Meta monetizes through internal AI products</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>xAI (Grok)</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>~10-20T (Grok 4/5 family)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>$200-500M</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>~0.5-1T (post-training alignment)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>$50-100M</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>~200-500T (X platform + API + enterprise)</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>$0.5-2B (est.)</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>~50-150T (Grok reasoning)</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>$0.2-0.5B (est.)</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>$0.7-2.5B</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Colossus 2 with 550K GPUs; primarily X platform + government contracts ($0.42/agency GSA deal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>~5-10T (Mistral Large, Medium, Small)</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>$50-150M</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>~0.2-0.5T</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>$10-30M</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>~100-300T</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>$0.3-0.6B (est.)</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>~20-50T</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>$0.05-0.15B (est.)</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>$0.35-0.75B</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>European provider; multi-cloud distribution (Azure, GCP, self-hosted); growing enterprise presence</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>~15-20T (V3, R1 family)</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>$10-30M (controversially low)</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>~1-3T (reinforcement learning for R1)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>$5-20M</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>~400-800T (API + self-hosted)</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>$0.2-0.5B</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>~200-400T (R1 reasoning)</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>$0.3-0.7B</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>$0.5-1.2B</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Disruptive pricing (90% below Western peers); R1 at $2.19/1M output tokens; heavy China + global adoption</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1"/>
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>SECTION C: Estimated Revenue by Token Type by Hyperscaler (Annual, 2025-2026)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
+      <c r="I18" s="6" t="n"/>
+      <c r="J18" s="6" t="n"/>
+      <c r="K18" s="6" t="n"/>
+    </row>
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Hyperscaler</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>Pre-Training Revenue
+(Selling compute to model cos.)</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>Post-Training Revenue
+(Fine-tuning services + compute)</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>Single-Shot Inference Revenue
+(API serving + managed inference)</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="inlineStr">
+        <is>
+          <t>Reasoning Inference Revenue
+(Reasoning model serving)</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="inlineStr">
+        <is>
+          <t>Total AI Services Revenue
+(Est. 2025)</t>
+        </is>
+      </c>
+      <c r="G19" s="1" t="inlineStr">
+        <is>
+          <t>Total AI CapEx (2026)</t>
+        </is>
+      </c>
+      <c r="H19" s="1" t="inlineStr">
+        <is>
+          <t>Key Model Partners
+(Training)</t>
+        </is>
+      </c>
+      <c r="I19" s="1" t="inlineStr">
+        <is>
+          <t>Key Model Partners
+(Inference)</t>
+        </is>
+      </c>
+      <c r="J19" s="1" t="inlineStr">
+        <is>
+          <t>Revenue per $1 CapEx</t>
+        </is>
+      </c>
+      <c r="K19" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft Azure</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>$4-6B
+(OpenAI training, Anthropic $30B commit, Mistral)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>$1-2B
+(Azure OpenAI fine-tuning, Azure ML custom training)</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>$5-8B
+(Azure OpenAI Service standard models, Copilot backend)</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>$2-4B
+(o1/o3 serving via Azure OpenAI, high-value enterprise)</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>$12-20B
+(Azure AI run rate ~$13B+; total Intelligent Cloud $131B ARR)</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>$100-145B</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI (exclusive primary), Anthropic, Mistral</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI (exclusive stateless API), Anthropic, Mistral, Meta (Llama), xAI</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>~$0.10-0.15</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI $250B cloud commitment; 45% of $625B RPO tied to OpenAI; Azure AI grew 39% YoY; hosts highest-revenue reasoning models (o1/o3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>AWS (Amazon)</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>$3-5B
+(Anthropic training on Trainium, OpenAI Frontier capacity, Nova training)</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>$0.5-1.5B
+(Bedrock fine-tuning, SageMaker training jobs, RFT)</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>$4-7B
+(Bedrock inference, SageMaker endpoints, Amazon Nova)</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>$1-2B
+(Bedrock reasoning models, Claude extended thinking)</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>$9-15B
+(AWS AI services; custom silicon &gt;$10B ARR; total AWS $142B ARR)</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>~$200B</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Anthropic (primary), OpenAI (Trainium), Amazon Nova (internal)</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Anthropic, OpenAI (Frontier), Meta (Llama), Mistral, DeepSeek (R1)</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>~$0.05-0.08</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Largest capex spender; Trainium/Inferentia custom chips &gt;$10B ARR with triple-digit growth; exclusive 3P cloud for OpenAI Frontier; Project Rainier for Anthropic</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Google Cloud (GCP)</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>$3-5B
+(Gemini training internally, Anthropic TPU allocation up to 1M TPUs)</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>$0.5-1B
+(Vertex AI tuning, Gemini tuning services)</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>$8-12B
+(Gemini API + Search AI + Workspace AI + Vertex AI inference)</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>$2-4B
+(Gemini thinking mode, Search reasoning, Vertex reasoning endpoints)</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>$14-22B
+(Google Cloud $71B ARR; AI embedded across Google products)</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>$175-185B</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Google/DeepMind (Gemini, internal), Anthropic</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Gemini (internal), Anthropic, Mistral, Meta (Llama)</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>~$0.08-0.12</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Largest token volume (1.3Q/month) but most revenue is embedded/internal; 48% cloud growth (fastest); TPU advantage for both training and inference; Gemini processes 7B tokens/min via API</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Oracle Cloud (OCI)</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>$0.5-1B
+(xAI Grok training partnership)</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>$0.1-0.3B
+(Limited fine-tuning offerings)</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>$0.3-0.7B
+(OCI Generative AI service, Grok inference)</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>$0.1-0.3B
+(Grok reasoning model serving)</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>$1-2.5B
+(est.; OCI growing rapidly but from smaller base)</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>~$50B</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>xAI (Grok)</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>xAI (Grok), limited third-party models</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>~$0.02-0.05</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Fastest-growing cloud for AI from small base; key xAI/Grok partnership; sovereign cloud positioning; zero data retention for enterprise</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Meta (Internal Infra)</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>$4-8B
+(Llama 4.x training on internal GPU clusters)</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>$0.5-1B
+(Internal RLHF, alignment, safety training)</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>N/A (internal consumption)
+Open-weight: enables ~$5-10B of 3P inference revenue</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>N/A (internal consumption)
+Open-weight: enables ~$1-3B of 3P reasoning revenue</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>N/A (no external cloud revenue;
+Llama enables ~$6-13B ecosystem revenue)</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>$115-135B</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Internal (Llama, Meta AI)</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>N/A (open-weight; 3P hosts: AWS, Azure, GCP)</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>N/A (internal)</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>No cloud revenue; invests heavily for internal AI products (Meta AI, Instagram, WhatsApp AI); Llama ecosystem generates revenue for other hyperscalers</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL (All Hyperscalers)</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>$15-25B</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>$3-6B</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>$17-28B (excl. Meta internal)</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>$5-11B</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>$36-60B (direct AI services revenue)</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>$640-715B</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>~$0.04-0.08</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Only ~$0.04 of every $1 capex converts to direct AI revenue; inference dominates revenue; reasoning is highest margin per token</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="60" customHeight="1"/>
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>SECTION D: Per-Token Pricing by Type Across Providers ($/1M Tokens, Feb 2026)</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
+      <c r="I27" s="6" t="n"/>
+      <c r="J27" s="6" t="n"/>
+      <c r="K27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Provider / Model</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>Token Type</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="inlineStr">
+        <is>
+          <t>Input ($/1M)</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="inlineStr">
+        <is>
+          <t>Output ($/1M)</t>
+        </is>
+      </c>
+      <c r="E28" s="1" t="inlineStr">
+        <is>
+          <t>Reasoning Output ($/1M)</t>
+        </is>
+      </c>
+      <c r="F28" s="1" t="inlineStr">
+        <is>
+          <t>Fine-Tuning Training ($/1M)</t>
+        </is>
+      </c>
+      <c r="G28" s="1" t="inlineStr">
+        <is>
+          <t>Fine-Tuned Hosting ($/mo)</t>
+        </is>
+      </c>
+      <c r="H28" s="1" t="inlineStr">
+        <is>
+          <t>Batch Discount</t>
+        </is>
+      </c>
+      <c r="I28" s="1" t="inlineStr">
+        <is>
+          <t>Cached Input ($/1M)</t>
+        </is>
+      </c>
+      <c r="J28" s="1" t="inlineStr">
+        <is>
+          <t>Cloud Availability</t>
+        </is>
+      </c>
+      <c r="K28" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI GPT-4.1-nano</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Single-Shot</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>$0.10</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>$0.40</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>$0.025</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Azure, AWS, Direct</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Budget tier</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>OpenAI GPT-4.1</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Single-Shot</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>$1.25</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>$10.00</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>$6.00 input / $6.00 output</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>$1,836/mo (Azure)</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>$0.625</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>Azure, AWS, Direct</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>Mid-tier production</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI o3</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>$2.00</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>$8.00</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>$8.00 (included in output)</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>$1.00</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>Azure, AWS, Direct</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>80% price drop Jun 2025; reasoning tokens billed as output</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>OpenAI o1</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>$3.00</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>$15.00</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>$15.00 (included in output)</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>$1.50</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>Azure, AWS, Direct</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>Original reasoning model; reasoning tokens 3-50x standard output</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI o4-mini</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>$1.10</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>$4.40</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>$4.40 (included in output)</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>RFT: $100/hr</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>$0.275</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>Azure, AWS, Direct</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>Budget reasoning model; RFT available</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Anthropic Claude Sonnet 4.5</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Single-Shot</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>$3.00</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>$15.00</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Limited availability</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>$0.30 (cached)</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>Azure, AWS, GCP, Direct</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Extended thinking adds reasoning tokens</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Anthropic Claude Opus 4.5</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Single-Shot + Thinking</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>$5.00</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>$25.00</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>$25.00 (thinking tokens)</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Limited</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>$0.50 (cached)</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>Azure, AWS, GCP, Direct</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Extended thinking mode generates hidden reasoning tokens</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Google Gemini Flash Lite</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Single-Shot</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>$0.10</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>$0.40</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>GCP, Direct</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>Ultra-budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini 3.0 Flash</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Single-Shot</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>$3.00</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Not available (Gemini 2.x)</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>GCP, Direct</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>Fast inference</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Google Gemini 3.0 Pro</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Single-Shot + Thinking</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>$2.00</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>$12.00</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>$12.00 (thinking mode)</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Not available (Gemini 2.x)</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>$0.50 (cached)</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>GCP, Direct</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>Thinking mode available</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek-R1</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>$0.55</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>$2.19</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>$2.19 (CoT included)</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>$0.14 (cached)</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>AWS (Bedrock), Direct</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>96% cheaper than o1; disruptive pricing</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>DeepSeek Chat V3.2</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Single-Shot</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>$0.27</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>$1.10</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>$0.07 (cached)</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>Lowest-cost competitive model</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Meta Llama 4 (via AWS Bedrock)</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Single-Shot</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>~$0.50-2.00 (varies)</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>~$1.50-6.00 (varies)</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Bedrock fine-tuning available</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Open-weight; pricing set by cloud provider</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>xAI Grok 4.1 Fast</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Single-Shot</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>$0.60</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>$4.00</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>OCI, Azure (Copilot)</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>Enterprise + X platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="60" customHeight="1"/>
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>SECTION E: Revenue Mix Summary by Token Type (2025 Est.)</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="n"/>
+      <c r="C44" s="6" t="n"/>
+      <c r="D44" s="6" t="n"/>
+      <c r="E44" s="6" t="n"/>
+      <c r="F44" s="6" t="n"/>
+      <c r="G44" s="6" t="n"/>
+      <c r="H44" s="6" t="n"/>
+      <c r="I44" s="6" t="n"/>
+      <c r="J44" s="6" t="n"/>
+      <c r="K44" s="6" t="n"/>
+    </row>
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>Token Type</t>
+        </is>
+      </c>
+      <c r="B45" s="1" t="inlineStr">
+        <is>
+          <t>Azure Revenue</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t>Azure % Mix</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="inlineStr">
+        <is>
+          <t>AWS Revenue</t>
+        </is>
+      </c>
+      <c r="E45" s="1" t="inlineStr">
+        <is>
+          <t>AWS % Mix</t>
+        </is>
+      </c>
+      <c r="F45" s="1" t="inlineStr">
+        <is>
+          <t>GCP Revenue</t>
+        </is>
+      </c>
+      <c r="G45" s="1" t="inlineStr">
+        <is>
+          <t>GCP % Mix</t>
+        </is>
+      </c>
+      <c r="H45" s="1" t="inlineStr">
+        <is>
+          <t>OCI Revenue</t>
+        </is>
+      </c>
+      <c r="I45" s="1" t="inlineStr">
+        <is>
+          <t>OCI % Mix</t>
+        </is>
+      </c>
+      <c r="J45" s="1" t="inlineStr">
+        <is>
+          <t>Total Market</t>
+        </is>
+      </c>
+      <c r="K45" s="1" t="inlineStr">
+        <is>
+          <t>Key Insight</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Pre-Training (Compute Sales)</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>$4-6B</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>25-35%</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>$3-5B</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>25-35%</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>$3-5B</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>20-25%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>$0.5-1B</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>30-45%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>$15-25B</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>High ASP per engagement; lumpy/project-based; dominated by large model company contracts</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Post-Training (Fine-Tuning)</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>$1-2B</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>8-12%</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>$0.5-1.5B</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>5-10%</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>$0.5-1B</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>3-5%</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>$0.1-0.3B</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>5-12%</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>$3-6B</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>Fastest-growing segment (30-35% CAGR); enterprise demand driving adoption; shift to token-based billing</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Single-Shot Inference</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>$5-8B</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>35-45%</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>$4-7B</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>40-50%</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>$8-12B</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>50-60%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>$0.3-0.7B</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>25-35%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>$17-28B</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>Largest revenue segment; price competition intense; bulk of enterprise API consumption; Google dominates volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Reasoning Inference</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>$2-4B</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>15-25%</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>$1-2B</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>10-15%</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>$2-4B</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>12-20%</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>$0.1-0.3B</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>5-15%</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>$5-11B</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>Highest margin per token; fastest inference growth (35-40% CAGR); Azure leads via exclusive o1/o3 hosting; agents multiply consumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>TOTAL AI Services Revenue</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>$12-20B</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>$9-15B</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>$14-22B</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>$1-2.5B</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>$36-60B</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Google highest by volume (embedded products); Azure highest per-token margin (reasoning); AWS broadest model catalog</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A18:K18"/>
+    <mergeCell ref="A44:K44"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A27:K27"/>
+    <mergeCell ref="A8:K8"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M18"/>
@@ -2896,7 +5408,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3344,7 +5856,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4168,7 +6680,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4430,7 +6942,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4768,7 +7280,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5070,7 +7582,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
